--- a/planning/떡메모지_비용효과.xlsx
+++ b/planning/떡메모지_비용효과.xlsx
@@ -554,22 +554,26 @@
           <t>지난 주문 (2025-09-04)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
+      <c r="B5" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>100</v>
+      </c>
       <c r="D5" s="5" t="n">
         <v>579810</v>
       </c>
       <c r="E5" s="6">
-        <f>F5*100</f>
+        <f>D5/B5</f>
         <v/>
       </c>
       <c r="F5" s="6">
-        <f>D5/50000</f>
+        <f>D5/(B5*C5)</f>
         <v/>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>총 50,000매·2건. 권당은 100매 1권으로 환산(추정). 배송료 58,500원 별도 표시</t>
+          <t>50,000매 × 2건 = 100,000매 = 100매 1,000권(대표 확인 10/21). 배송료 58,500원 별도 표시</t>
         </is>
       </c>
     </row>
@@ -605,16 +609,18 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>견적 입력: 100권</t>
+          <t>견적: 1,000권 (500권×2건)</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="D7" s="7" t="n"/>
+      <c r="D7" s="7" t="n">
+        <v>560450</v>
+      </c>
       <c r="E7" s="6">
         <f>IF(D7="","",D7/B7)</f>
         <v/>
@@ -625,18 +631,18 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>사이트에서 확인 후 입력</t>
+          <t>10/21 캡처. 공급가 509,500 + VAT 50,950. 2건 = 디자인 2종 가능</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>견적 입력: 300권</t>
+          <t>견적 입력: 500권 (1건)</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>100</v>
@@ -652,18 +658,18 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>사이트에서 확인 후 입력</t>
+          <t>사이트에서 확인 후 입력 (추정: 1,000권의 절반 약 280,225원)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>견적 입력: 500권</t>
+          <t>견적 입력: 300권 (1건)</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>100</v>
@@ -686,7 +692,7 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>읽는 법: 수량이 많을수록 권당 단가가 크게 내려갑니다(10권 4,675원/권 vs 지난 대량 주문 환산 약 1,160원/권). 남은 권은 매장·온라인 주문 덤으로 쓰도록 디자인에 날짜를 넣지 않습니다.</t>
+          <t>읽는 법: 10권은 권당 4,675원, 1,000권은 권당 약 560원. 남은 권은 매장·온라인 주문 덤으로 쓰도록 디자인에 날짜를 넣지 않습니다.</t>
         </is>
       </c>
     </row>
